--- a/DataTable/files/VegetablesProduction.xlsx
+++ b/DataTable/files/VegetablesProduction.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\OneDrive\Documents\GitHub\UiPath\DataTable\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C66750E-95CC-4083-8692-8991369F0D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E167085E-ED5C-4AD5-96A2-0F7F63451DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7176" yWindow="1056" windowWidth="12120" windowHeight="8592" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tracker" sheetId="2" r:id="rId1"/>
+    <sheet name="Totals" sheetId="3" r:id="rId1"/>
+    <sheet name="Tracker" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="40">
   <si>
     <t>Vegetables</t>
   </si>
@@ -142,6 +143,9 @@
   </si>
   <si>
     <t>June</t>
+  </si>
+  <si>
+    <t>TotalPrice</t>
   </si>
 </sst>
 </file>
@@ -458,6 +462,867 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83075C51-4F63-4819-B2E7-6F7089135192}">
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>782</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>1.3</v>
+      </c>
+      <c r="G2">
+        <v>1016.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>903</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>1.3</v>
+      </c>
+      <c r="G3">
+        <v>1173.9000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>767</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>1.3</v>
+      </c>
+      <c r="G4">
+        <v>997.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>921</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>1.6</v>
+      </c>
+      <c r="G5">
+        <v>1473.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>613</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>1.6</v>
+      </c>
+      <c r="G6">
+        <v>980.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>948</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>1.6</v>
+      </c>
+      <c r="G7">
+        <v>1516.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>713</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G8">
+        <v>1568.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>223</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G9">
+        <v>490.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>528</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G10">
+        <v>1161.5999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>324</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G11">
+        <v>712.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>187</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G12">
+        <v>411.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>105</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G13">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14">
+        <v>648</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14">
+        <v>2.7</v>
+      </c>
+      <c r="G14">
+        <v>1749.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15">
+        <v>246</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15">
+        <v>2.7</v>
+      </c>
+      <c r="G15">
+        <v>664.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>539</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16">
+        <v>2.7</v>
+      </c>
+      <c r="G16">
+        <v>1455.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>573</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17">
+        <v>3.3</v>
+      </c>
+      <c r="G17">
+        <v>1890.8999999999901</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>782</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18">
+        <v>3.3</v>
+      </c>
+      <c r="G18">
+        <v>2580.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>868</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19">
+        <v>3.3</v>
+      </c>
+      <c r="G19">
+        <v>2864.3999999999901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20">
+        <v>278</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20">
+        <v>3.8</v>
+      </c>
+      <c r="G20">
+        <v>1056.3999999999901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>455</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <v>3.8</v>
+      </c>
+      <c r="G21">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <v>279</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22">
+        <v>3.8</v>
+      </c>
+      <c r="G22">
+        <v>1060.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23">
+        <v>456</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G23">
+        <v>2006.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24">
+        <v>798</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G24">
+        <v>3511.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G25">
+        <v>633.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26">
+        <v>556</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G26">
+        <v>2724.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <v>325</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G27">
+        <v>1592.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>876</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G28">
+        <v>4292.3999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29">
+        <v>889</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29">
+        <v>5.5</v>
+      </c>
+      <c r="G29">
+        <v>4889.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30">
+        <v>129</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30">
+        <v>5.5</v>
+      </c>
+      <c r="G30">
+        <v>709.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31">
+        <v>687</v>
+      </c>
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31">
+        <v>5.5</v>
+      </c>
+      <c r="G31">
+        <v>3778.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32">
+        <v>996</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32">
+        <v>5.5</v>
+      </c>
+      <c r="G32">
+        <v>5478</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33">
+        <v>679</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33">
+        <v>5.5</v>
+      </c>
+      <c r="G33">
+        <v>3734.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34">
+        <v>253</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34">
+        <v>5.5</v>
+      </c>
+      <c r="G34">
+        <v>1391.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35">
+        <v>135</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35">
+        <v>6.6</v>
+      </c>
+      <c r="G35">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36">
+        <v>425</v>
+      </c>
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36">
+        <v>6.6</v>
+      </c>
+      <c r="G36">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37">
+        <v>625</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37">
+        <v>6.6</v>
+      </c>
+      <c r="G37">
+        <v>4125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1699EE-F9FA-448C-9BE4-8BAAD65083F8}">
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
